--- a/documentation/Tables in Tex.xlsx
+++ b/documentation/Tables in Tex.xlsx
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B17:J41"/>
+  <dimension ref="B17:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -642,6 +642,11 @@
       </c>
       <c r="D41" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
